--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7c46d025543e43b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5db84dde0b77492f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5db84dde0b77492f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3463dc1d5f1c46b6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3463dc1d5f1c46b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re63ce8158553403e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re63ce8158553403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f9e020685e94cd2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f9e020685e94cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0037f1b86e7448b9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0037f1b86e7448b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe7772d7d9dd4102"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe7772d7d9dd4102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R15dacd83deee44f3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R15dacd83deee44f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3dc401186f094c59"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3dc401186f094c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73d5d812887c4755"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73d5d812887c4755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd947e6784ac74ce2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd947e6784ac74ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R440f38b5f5d44555"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R440f38b5f5d44555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R58a377a9530a40ba"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R58a377a9530a40ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R98c0bf4c619a4ba7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R98c0bf4c619a4ba7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca2da3a5961a459c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca2da3a5961a459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc075819a6fb54898"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc075819a6fb54898"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c4b4c4cfe1648b9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c4b4c4cfe1648b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra49e26a89cfd47e7"/>
   </x:sheets>
 </x:workbook>
 </file>
